--- a/artfynd/A 27663-2026 artfynd.xlsx
+++ b/artfynd/A 27663-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135448018</v>
+        <v>135471088</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -704,24 +704,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472310</v>
+        <v>472526</v>
       </c>
       <c r="R2" t="n">
-        <v>6550357</v>
+        <v>6550589</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -748,27 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack med stelnade kåda i hackringarna. Syns tydligt med kikare ca 4-5 m upp. Gran märkt med rött band. Svårt med fotoljuset pga sol.</t>
+          <t>Födohack vid basen av död tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135448475</v>
+        <v>135448018</v>
       </c>
       <c r="B3" t="n">
         <v>57975</v>
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472327</v>
+        <v>472310</v>
       </c>
       <c r="R3" t="n">
-        <v>6550486</v>
+        <v>6550357</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack med stelnade kåda i hackhålen. Små hackhål på rad. Syns med kikare ca 1 m ovanför sveaskogs snitsling.</t>
+          <t>Ringhack med stelnade kåda i hackringarna. Syns tydligt med kikare ca 4-5 m upp. Gran märkt med rött band. Svårt med fotoljuset pga sol.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,59 +912,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135449588</v>
+        <v>135448475</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472554</v>
+        <v>472327</v>
       </c>
       <c r="R4" t="n">
-        <v>6550431</v>
+        <v>6550486</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -999,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1000,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt på sten på häll men även på hällen</t>
+          <t>Ringhack med stelnade kåda i hackhålen. Små hackhål på rad. Syns med kikare ca 1 m ovanför sveaskogs snitsling.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135449664</v>
+        <v>135449588</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1069,7 +1060,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472574</v>
+        <v>472554</v>
       </c>
       <c r="R5" t="n">
-        <v>6550424</v>
+        <v>6550431</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På rotvälta</t>
+          <t>Rikligt på sten på häll men även på hällen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135449896</v>
+        <v>135449664</v>
       </c>
       <c r="B6" t="n">
-        <v>4776</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,27 +1169,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472610</v>
+        <v>472574</v>
       </c>
       <c r="R6" t="n">
-        <v>6550384</v>
+        <v>6550424</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Och kläckhål</t>
+          <t>På rotvälta</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135449915</v>
+        <v>135470977</v>
       </c>
       <c r="B7" t="n">
-        <v>98060</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,34 +1286,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472618</v>
+        <v>472513</v>
       </c>
       <c r="R7" t="n">
-        <v>6550376</v>
+        <v>6550575</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Laxå</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1335,27 +1340,32 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Skagershult</t>
+          <t>Nysund</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,6 +1389,989 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135471892</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>472441</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6550340</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På häll.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135449896</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>472610</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6550384</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135449915</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>472618</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6550376</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135470930</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>472506</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6550575</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135470999</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>472527</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6550579</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135471062</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>472518</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6550601</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135471959</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>472438</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6550456</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135470951</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>472511</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6550575</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135471033</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>472516</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6550601</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27663-2026 artfynd.xlsx
+++ b/artfynd/A 27663-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471088</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448475</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1155,6 +1175,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135449588</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135449664</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470977</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471892</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1623,6 +1663,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135449896</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1730,6 +1775,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135449915</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1837,6 +1887,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470930</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1944,6 +1999,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470999</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2051,6 +2111,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471062</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2158,6 +2223,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471959</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2265,6 +2335,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470951</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2372,8 +2447,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471033</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27663-2026 artfynd.xlsx
+++ b/artfynd/A 27663-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135471088</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135448018</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135448475</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>135449588</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>135449664</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>135470977</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>135471892</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>135449915</v>
       </c>
       <c r="B10" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>135470930</v>
       </c>
       <c r="B11" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>135470999</v>
       </c>
       <c r="B12" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>135471062</v>
       </c>
       <c r="B13" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>135471959</v>
       </c>
       <c r="B14" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>135470951</v>
       </c>
       <c r="B15" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135471033</v>
       </c>
       <c r="B16" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27663-2026 artfynd.xlsx
+++ b/artfynd/A 27663-2026 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>135449915</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>135470930</v>
       </c>
       <c r="B11" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>135470999</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>135471062</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>135471959</v>
       </c>
       <c r="B14" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>135470951</v>
       </c>
       <c r="B15" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>135471033</v>
       </c>
       <c r="B16" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27663-2026 artfynd.xlsx
+++ b/artfynd/A 27663-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,27 +802,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135448018</v>
+        <v>135914320</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,24 +831,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472310</v>
+        <v>472538</v>
       </c>
       <c r="R3" t="n">
-        <v>6550357</v>
+        <v>6550427</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -875,27 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack med stelnade kåda i hackringarna. Syns tydligt med kikare ca 4-5 m upp. Gran märkt med rött band. Svårt med fotoljuset pga sol.</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,16 +913,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135448018</t>
+          <t>https://artportalen.se/Sighting/135914320</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135448475</v>
+        <v>135914165</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,16 +930,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,24 +948,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472327</v>
+        <v>472538</v>
       </c>
       <c r="R4" t="n">
-        <v>6550486</v>
+        <v>6550427</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1000,27 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack med stelnade kåda i hackhålen. Små hackhål på rad. Syns med kikare ca 1 m ovanför sveaskogs snitsling.</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,65 +1030,59 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135448475</t>
+          <t>https://artportalen.se/Sighting/135914165</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135449588</v>
+        <v>135448018</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472554</v>
+        <v>472310</v>
       </c>
       <c r="R5" t="n">
-        <v>6550431</v>
+        <v>6550357</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1136,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1146,12 +1124,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på sten på häll men även på hällen</t>
+          <t>Ringhack med stelnade kåda i hackringarna. Syns tydligt med kikare ca 4-5 m upp. Gran märkt med rött band. Svårt med fotoljuset pga sol.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,56 +1155,59 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135449588</t>
+          <t>https://artportalen.se/Sighting/135448018</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135449664</v>
+        <v>135448475</v>
       </c>
       <c r="B6" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472574</v>
+        <v>472327</v>
       </c>
       <c r="R6" t="n">
-        <v>6550424</v>
+        <v>6550486</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1258,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1249,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På rotvälta</t>
+          <t>Ringhack med stelnade kåda i hackhålen. Små hackhål på rad. Syns med kikare ca 1 m ovanför sveaskogs snitsling.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,13 +1280,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135449664</t>
+          <t>https://artportalen.se/Sighting/135448475</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135470977</v>
+        <v>135449588</v>
       </c>
       <c r="B7" t="n">
         <v>57167</v>
@@ -1333,7 +1314,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -1341,14 +1331,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472513</v>
+        <v>472554</v>
       </c>
       <c r="R7" t="n">
-        <v>6550575</v>
+        <v>6550431</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1375,27 +1365,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Rikligt på sten på häll men även på hällen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,13 +1411,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470977</t>
+          <t>https://artportalen.se/Sighting/135449588</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135471892</v>
+        <v>135449664</v>
       </c>
       <c r="B8" t="n">
         <v>57167</v>
@@ -1467,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472441</v>
+        <v>472574</v>
       </c>
       <c r="R8" t="n">
-        <v>6550340</v>
+        <v>6550424</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1497,27 +1487,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På häll.</t>
+          <t>På rotvälta</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,16 +1533,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471892</t>
+          <t>https://artportalen.se/Sighting/135449664</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135449896</v>
+        <v>135470977</v>
       </c>
       <c r="B9" t="n">
-        <v>4776</v>
+        <v>57167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,39 +1550,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472610</v>
+        <v>472513</v>
       </c>
       <c r="R9" t="n">
-        <v>6550384</v>
+        <v>6550575</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1619,27 +1609,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Och kläckhål</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,16 +1655,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135449896</t>
+          <t>https://artportalen.se/Sighting/135470977</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135449915</v>
+        <v>135471892</v>
       </c>
       <c r="B10" t="n">
-        <v>98136</v>
+        <v>57167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,34 +1672,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472618</v>
+        <v>472441</v>
       </c>
       <c r="R10" t="n">
-        <v>6550376</v>
+        <v>6550340</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1721,7 +1716,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Laxå</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1731,27 +1726,32 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Skagershult</t>
+          <t>Nysund</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På häll.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1777,16 +1777,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135449915</t>
+          <t>https://artportalen.se/Sighting/135471892</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135470930</v>
+        <v>135449896</v>
       </c>
       <c r="B11" t="n">
-        <v>98136</v>
+        <v>4776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,34 +1794,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472506</v>
+        <v>472610</v>
       </c>
       <c r="R11" t="n">
-        <v>6550575</v>
+        <v>6550384</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1848,22 +1853,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Och kläckhål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,51 +1899,56 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470930</t>
+          <t>https://artportalen.se/Sighting/135449896</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135470999</v>
+        <v>135914275</v>
       </c>
       <c r="B12" t="n">
-        <v>98136</v>
+        <v>58524</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>102990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472527</v>
+        <v>472538</v>
       </c>
       <c r="R12" t="n">
-        <v>6550579</v>
+        <v>6550427</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1960,22 +1975,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>04:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>04:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,51 +2016,56 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470999</t>
+          <t>https://artportalen.se/Sighting/135914275</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135471062</v>
+        <v>135914230</v>
       </c>
       <c r="B13" t="n">
-        <v>98136</v>
+        <v>58139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>103020</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472518</v>
+        <v>472538</v>
       </c>
       <c r="R13" t="n">
-        <v>6550601</v>
+        <v>6550427</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2072,22 +2092,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,51 +2133,56 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471062</t>
+          <t>https://artportalen.se/Sighting/135914230</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135471959</v>
+        <v>135914516</v>
       </c>
       <c r="B14" t="n">
-        <v>98136</v>
+        <v>58141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472438</v>
+        <v>472538</v>
       </c>
       <c r="R14" t="n">
-        <v>6550456</v>
+        <v>6550427</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2184,22 +2209,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,16 +2250,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471959</t>
+          <t>https://artportalen.se/Sighting/135914516</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135470951</v>
+        <v>135914637</v>
       </c>
       <c r="B15" t="n">
-        <v>98139</v>
+        <v>58136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,34 +2267,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>103023</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472511</v>
+        <v>472538</v>
       </c>
       <c r="R15" t="n">
-        <v>6550575</v>
+        <v>6550427</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2296,22 +2326,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2337,16 +2367,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135470951</t>
+          <t>https://artportalen.se/Sighting/135914637</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135471033</v>
+        <v>135449915</v>
       </c>
       <c r="B16" t="n">
-        <v>98139</v>
+        <v>98138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,16 +2384,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2374,14 +2404,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472516</v>
+        <v>472618</v>
       </c>
       <c r="R16" t="n">
-        <v>6550601</v>
+        <v>6550376</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2393,7 +2423,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Laxå</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2403,27 +2433,27 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Nysund</t>
+          <t>Skagershult</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2448,6 +2478,678 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135449915</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135470930</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>472506</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6550575</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470930</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135470999</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>472527</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6550579</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470999</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135471062</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>472518</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6550601</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471062</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135471959</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Trollkarlsberget, Trollkarlsberget, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>472438</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6550456</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471959</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135470951</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98141</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>472511</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6550575</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470951</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135471033</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98141</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bergslagsleden, Bergslagsleden, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>472516</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6550601</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135471033</t>
         </is>
@@ -2470,6 +3172,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
